--- a/insurance_data/5_savings/savings/extracted_data.xlsx
+++ b/insurance_data/5_savings/savings/extracted_data.xlsx
@@ -57616,7 +57616,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>(무) 모아Rich저축보험2601 (월납)</t>
+          <t>(무) 모아Rich저축보험2605 (월납)</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -57631,27 +57631,27 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>6,895,000</t>
+          <t>6,900,000</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>6,229,000</t>
+          <t>6,234,000</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>6,895,000</t>
+          <t>6,900,000</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="J287" t="inlineStr"/>
@@ -57673,7 +57673,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>(무) 모아Rich저축보험2601</t>
+          <t>(무) 모아Rich저축보험2605</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -57688,12 +57688,12 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
@@ -57703,32 +57703,32 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>6,895,000</t>
+          <t>6,900,000</t>
         </is>
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>6,229,000</t>
+          <t>6,234,000</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>6,895,000</t>
+          <t>6,900,000</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
         <is>
-          <t>6,229,000</t>
+          <t>6,234,000</t>
         </is>
       </c>
       <c r="AE287" t="inlineStr"/>
@@ -57760,7 +57760,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>(무) 모아Rich저축보험2601 (월납)</t>
+          <t>(무) 모아Rich저축보험2605 (월납)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -57775,27 +57775,27 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>21,083,000</t>
+          <t>21,130,000</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>20,638,000</t>
+          <t>20,685,000</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>21,083,000</t>
+          <t>21,130,000</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="J288" t="inlineStr"/>
@@ -57824,12 +57824,12 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="X288" t="inlineStr">
@@ -57839,32 +57839,32 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>21,083,000</t>
+          <t>21,130,000</t>
         </is>
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>20,638,000</t>
+          <t>20,685,000</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>21,083,000</t>
+          <t>21,130,000</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AD288" t="inlineStr">
         <is>
-          <t>20,638,000</t>
+          <t>20,685,000</t>
         </is>
       </c>
       <c r="AE288" t="inlineStr"/>
@@ -57896,7 +57896,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>(무) 모아Rich저축보험2601 (월납)</t>
+          <t>(무) 모아Rich저축보험2605 (월납)</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -57911,27 +57911,27 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>35,814,000</t>
+          <t>35,948,000</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>35,592,000</t>
+          <t>35,726,000</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>35,814,000</t>
+          <t>35,948,000</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="J289" t="inlineStr"/>
@@ -57955,17 +57955,17 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
@@ -57975,32 +57975,32 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>35,814,000</t>
+          <t>35,948,000</t>
         </is>
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>35,592,000</t>
+          <t>35,726,000</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>35,814,000</t>
+          <t>35,948,000</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
         <is>
-          <t>35,592,000</t>
+          <t>35,726,000</t>
         </is>
       </c>
       <c r="AE289" t="inlineStr"/>
@@ -58032,7 +58032,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>(무) 모아Rich저축보험2601 (월납)</t>
+          <t>(무) 모아Rich저축보험2605 (월납)</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -58047,27 +58047,27 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="J290" t="inlineStr"/>
@@ -58096,12 +58096,12 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="X290" t="inlineStr">
@@ -58111,32 +58111,32 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>75,562,000</t>
+          <t>76,140,000</t>
         </is>
       </c>
       <c r="AE290" t="inlineStr"/>
@@ -58168,7 +58168,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (월납)</t>
+          <t>드림모아저축보험 무배당2604 (월납)</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -58225,7 +58225,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601</t>
+          <t>드림모아저축보험 무배당2604</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -58312,7 +58312,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (월납)</t>
+          <t>드림모아저축보험 무배당2604 (월납)</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -58448,7 +58448,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (월납)</t>
+          <t>드림모아저축보험 무배당2604 (월납)</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -58584,7 +58584,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (월납)</t>
+          <t>드림모아저축보험 무배당2604 (월납)</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -58720,7 +58720,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (일시납)</t>
+          <t>드림모아저축보험 무배당2604 (일시납)</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -58777,7 +58777,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601</t>
+          <t>드림모아저축보험 무배당2604</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -58864,7 +58864,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (일시납)</t>
+          <t>드림모아저축보험 무배당2604 (일시납)</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -59000,7 +59000,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (일시납)</t>
+          <t>드림모아저축보험 무배당2604 (일시납)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -59136,7 +59136,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>드림모아저축보험 무배당2601 (일시납)</t>
+          <t>드림모아저축보험 무배당2604 (일시납)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
